--- a/students.xlsx
+++ b/students.xlsx
@@ -436,7 +436,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Ravi</t>
+          <t>Vijay</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -449,7 +449,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Kiran</t>
+          <t>Ajay</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -462,11 +462,11 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Suresh</t>
+          <t>Bunny</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C4" t="n">
         <v>78</v>
